--- a/assets/DPS_Code_allocation_table.xlsx
+++ b/assets/DPS_Code_allocation_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD25043-BD7C-4096-82F7-7BA392A988BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AA03DE-8D1E-4532-BEEA-383A4D6CB5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="764" xr2:uid="{09BBBF33-EBB5-4EDB-9CE7-7EB6A33B148E}"/>
   </bookViews>

--- a/assets/DPS_Code_allocation_table.xlsx
+++ b/assets/DPS_Code_allocation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AA03DE-8D1E-4532-BEEA-383A4D6CB5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6F330C-E3E1-4749-9949-DBC6034EBADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="764" xr2:uid="{09BBBF33-EBB5-4EDB-9CE7-7EB6A33B148E}"/>
   </bookViews>
